--- a/site/Dayforce-to-Salesforce-Contacts-Sync-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-to-Salesforce-Contacts-Sync-Integration-Guide/headings.xlsx
@@ -639,7 +639,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Integration Execution Features Settings</t>
+          <t>General Execution Features Settings</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -661,7 +661,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Contact Life Cycle Management</t>
+          <t>Manage Contacts Life Cycle Management</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">

--- a/site/Dayforce-to-Salesforce-Contacts-Sync-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-to-Salesforce-Contacts-Sync-Integration-Guide/headings.xlsx
@@ -661,7 +661,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Manage Contacts Life Cycle Management</t>
+          <t>Manage Contacts</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -683,7 +683,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Salesforce Settings Manage contact lifecycle management</t>
+          <t>Salesforce Settings Manage Contact Lifecycle Management</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">

--- a/site/Dayforce-to-Salesforce-Contacts-Sync-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-to-Salesforce-Contacts-Sync-Integration-Guide/headings.xlsx
@@ -639,7 +639,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>General Execution Features Settings</t>
+          <t>General Settings</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -683,7 +683,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Salesforce Settings Manage Contact Lifecycle Management</t>
+          <t>Manage Contact Lifecycle Management</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">

--- a/site/Dayforce-to-Salesforce-Contacts-Sync-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-to-Salesforce-Contacts-Sync-Integration-Guide/headings.xlsx
@@ -771,7 +771,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Debug Settings</t>
+          <t>Logging</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -781,188 +781,188 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KJ53FCW9MVRD5Y58BMAJGH9X</t>
+          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Salesforce-Contacts-Sync-Integration-Guide/#h_01KJ53FCW9MVRD5Y58BMAJGH9X</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Salesforce-Contacts-Sync-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>h_01KGHF59DA5EF0WXHK2SMFB9W4</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Salesforce-Contacts-Sync-Integration-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Salesforce-Contacts-Sync-Integration-Guide/#h_01KGHF59DA5EF0WXHK2SMFB9W4</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Notification Settings</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KGHF6DZYKTRFQSB4B1QVYWAS</t>
+          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Salesforce-Contacts-Sync-Integration-Guide/#h_01KGHF6DZYKTRFQSB4B1QVYWAS</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Salesforce-Contacts-Sync-Integration-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Logging</t>
+          <t>Notification Settings</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>h_01KGHF6DZYKTRFQSB4B1QVYWAS</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Salesforce-Contacts-Sync-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Salesforce-Contacts-Sync-Integration-Guide/#h_01KGHF6DZYKTRFQSB4B1QVYWAS</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Reporting</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KGHF59DA5EF0WXHK2SMFB9W4</t>
+          <t>01KG21C7RQCRB9NJP5ZN6VEHXX</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Salesforce-Contacts-Sync-Integration-Guide/#h_01KGHF59DA5EF0WXHK2SMFB9W4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Salesforce-Contacts-Sync-Integration-Guide/#01KG21C7RQCRB9NJP5ZN6VEHXX</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reporting</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>01KG21C7RQCRB9NJP5ZN6VEHXX</t>
+          <t>h_01KGHF9JDXCJXF0HYB7BRZ2P0E</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Salesforce-Contacts-Sync-Integration-Guide/#01KG21C7RQCRB9NJP5ZN6VEHXX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Salesforce-Contacts-Sync-Integration-Guide/#h_01KGHF9JDXCJXF0HYB7BRZ2P0E</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Log Insights</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KGHF9JDXCJXF0HYB7BRZ2P0E</t>
+          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Salesforce-Contacts-Sync-Integration-Guide/#h_01KGHF9JDXCJXF0HYB7BRZ2P0E</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Salesforce-Contacts-Sync-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Log Insights</t>
+          <t>Log Insight Settings</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>h_01KGHFA6Y71CG6DK6D0DZ6XTH1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Salesforce-Contacts-Sync-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Salesforce-Contacts-Sync-Integration-Guide/#h_01KGHFA6Y71CG6DK6D0DZ6XTH1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Log Insight Settings</t>
+          <t>Debug Mode</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01KGHFA6Y71CG6DK6D0DZ6XTH1</t>
+          <t>h_01KJ53FCW9MVRD5Y58BMAJGH9X</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Salesforce-Contacts-Sync-Integration-Guide/#h_01KGHFA6Y71CG6DK6D0DZ6XTH1</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-to-Salesforce-Contacts-Sync-Integration-Guide/#h_01KJ53FCW9MVRD5Y58BMAJGH9X</t>
         </is>
       </c>
     </row>
